--- a/research/traditional_assets/database/data/lithuania/lithuania_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/lithuania/lithuania_financial_svcs_non_bank_insurance.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.04112903225806451</v>
+        <v>0.07242424242424242</v>
       </c>
       <c r="H2">
-        <v>0.04112903225806451</v>
+        <v>0.07242424242424242</v>
       </c>
       <c r="I2">
-        <v>0.01989247311827957</v>
+        <v>0.07939393939393941</v>
       </c>
       <c r="J2">
-        <v>0.009946236559139784</v>
+        <v>0.0622585567909309</v>
       </c>
       <c r="K2">
-        <v>0.035</v>
+        <v>0.192</v>
       </c>
       <c r="L2">
-        <v>0.009408602150537635</v>
+        <v>0.05818181818181819</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,61 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>10.5</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="V2">
-        <v>0.7894736842105263</v>
+        <v>0.9346153846153846</v>
       </c>
       <c r="W2">
-        <v>0.02</v>
+        <v>0.08807339449541284</v>
       </c>
       <c r="X2">
-        <v>0.02535811930758778</v>
+        <v>0.05138203451548536</v>
       </c>
       <c r="Y2">
-        <v>-0.00535811930758778</v>
-      </c>
-      <c r="Z2">
-        <v>-0.8266666666666667</v>
-      </c>
-      <c r="AA2">
-        <v>-0.008222222222222221</v>
+        <v>0.03669135997992747</v>
       </c>
       <c r="AB2">
-        <v>0.02541248937737002</v>
-      </c>
-      <c r="AC2">
-        <v>-0.03363471159959224</v>
+        <v>0.05117551431462832</v>
       </c>
       <c r="AD2">
-        <v>1.28</v>
+        <v>0.99</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.28</v>
+        <v>0.99</v>
       </c>
       <c r="AG2">
-        <v>-9.220000000000001</v>
+        <v>-8.73</v>
       </c>
       <c r="AH2">
-        <v>0.08779149519890261</v>
+        <v>0.08691834942932396</v>
       </c>
       <c r="AI2">
-        <v>0.3699421965317919</v>
+        <v>0.2877906976744186</v>
       </c>
       <c r="AJ2">
-        <v>-2.259803921568627</v>
+        <v>-5.227544910179641</v>
       </c>
       <c r="AK2">
-        <v>1.309659090909091</v>
+        <v>1.390127388535032</v>
       </c>
       <c r="AL2">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>0.02</v>
+        <v>-0.017</v>
       </c>
       <c r="AN2">
-        <v>3.114355231143553</v>
-      </c>
-      <c r="AO2">
-        <v>3.7</v>
+        <v>3.03680981595092</v>
       </c>
       <c r="AP2">
-        <v>-22.4330900243309</v>
+        <v>-26.77914110429448</v>
       </c>
       <c r="AQ2">
-        <v>3.7</v>
+        <v>-15.41176470588235</v>
       </c>
     </row>
     <row r="3">
@@ -713,22 +701,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.04112903225806451</v>
+        <v>0.07242424242424242</v>
       </c>
       <c r="H3">
-        <v>0.04112903225806451</v>
+        <v>0.07242424242424242</v>
       </c>
       <c r="I3">
-        <v>0.01989247311827957</v>
+        <v>0.07939393939393941</v>
       </c>
       <c r="J3">
-        <v>0.009946236559139784</v>
+        <v>0.0622585567909309</v>
       </c>
       <c r="K3">
-        <v>0.035</v>
+        <v>0.192</v>
       </c>
       <c r="L3">
-        <v>0.009408602150537635</v>
+        <v>0.05818181818181819</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +740,61 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>10.5</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="V3">
-        <v>0.7894736842105263</v>
+        <v>0.9346153846153846</v>
       </c>
       <c r="W3">
-        <v>0.02</v>
+        <v>0.08807339449541284</v>
       </c>
       <c r="X3">
-        <v>0.02535811930758778</v>
+        <v>0.05138203451548536</v>
       </c>
       <c r="Y3">
-        <v>-0.00535811930758778</v>
-      </c>
-      <c r="Z3">
-        <v>-0.8266666666666667</v>
-      </c>
-      <c r="AA3">
-        <v>-0.008222222222222221</v>
+        <v>0.03669135997992747</v>
       </c>
       <c r="AB3">
-        <v>0.02541248937737002</v>
-      </c>
-      <c r="AC3">
-        <v>-0.03363471159959224</v>
+        <v>0.05117551431462832</v>
       </c>
       <c r="AD3">
-        <v>1.28</v>
+        <v>0.99</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.28</v>
+        <v>0.99</v>
       </c>
       <c r="AG3">
-        <v>-9.220000000000001</v>
+        <v>-8.73</v>
       </c>
       <c r="AH3">
-        <v>0.08779149519890261</v>
+        <v>0.08691834942932396</v>
       </c>
       <c r="AI3">
-        <v>0.3699421965317919</v>
+        <v>0.2877906976744186</v>
       </c>
       <c r="AJ3">
-        <v>-2.259803921568627</v>
+        <v>-5.227544910179641</v>
       </c>
       <c r="AK3">
-        <v>1.309659090909091</v>
+        <v>1.390127388535032</v>
       </c>
       <c r="AL3">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.02</v>
+        <v>-0.017</v>
       </c>
       <c r="AN3">
-        <v>3.114355231143553</v>
-      </c>
-      <c r="AO3">
-        <v>3.7</v>
+        <v>3.03680981595092</v>
       </c>
       <c r="AP3">
-        <v>-22.4330900243309</v>
+        <v>-26.77914110429448</v>
       </c>
       <c r="AQ3">
-        <v>3.7</v>
+        <v>-15.41176470588235</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/lithuania/lithuania_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/lithuania/lithuania_financial_svcs_non_bank_insurance.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.07242424242424242</v>
+        <v>0.04021739130434783</v>
       </c>
       <c r="H2">
-        <v>0.07242424242424242</v>
+        <v>0.04021739130434783</v>
       </c>
       <c r="I2">
-        <v>0.07939393939393941</v>
+        <v>0.07782608695652174</v>
       </c>
       <c r="J2">
-        <v>0.0622585567909309</v>
+        <v>0.06597854615999087</v>
       </c>
       <c r="K2">
-        <v>0.192</v>
+        <v>0.323</v>
       </c>
       <c r="L2">
-        <v>0.05818181818181819</v>
+        <v>0.07021739130434783</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,61 +627,61 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>9.720000000000001</v>
+        <v>9.82</v>
       </c>
       <c r="V2">
-        <v>0.9346153846153846</v>
+        <v>0.9177570093457945</v>
       </c>
       <c r="W2">
-        <v>0.08807339449541284</v>
+        <v>0.1318367346938775</v>
       </c>
       <c r="X2">
-        <v>0.05138203451548536</v>
+        <v>0.05681300993455153</v>
       </c>
       <c r="Y2">
-        <v>0.03669135997992747</v>
+        <v>0.07502372475932602</v>
       </c>
       <c r="AB2">
-        <v>0.05117551431462832</v>
+        <v>0.05593115147940682</v>
       </c>
       <c r="AD2">
-        <v>0.99</v>
+        <v>3.63</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.99</v>
+        <v>3.63</v>
       </c>
       <c r="AG2">
-        <v>-8.73</v>
+        <v>-6.19</v>
       </c>
       <c r="AH2">
-        <v>0.08691834942932396</v>
+        <v>0.2533147243545011</v>
       </c>
       <c r="AI2">
-        <v>0.2877906976744186</v>
+        <v>0.55</v>
       </c>
       <c r="AJ2">
-        <v>-5.227544910179641</v>
+        <v>-1.372505543237251</v>
       </c>
       <c r="AK2">
-        <v>1.390127388535032</v>
+        <v>1.922360248447205</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.017</v>
+        <v>-0.024</v>
       </c>
       <c r="AN2">
-        <v>3.03680981595092</v>
+        <v>7.484536082474227</v>
       </c>
       <c r="AP2">
-        <v>-26.77914110429448</v>
+        <v>-12.76288659793815</v>
       </c>
       <c r="AQ2">
-        <v>-15.41176470588235</v>
+        <v>-14.91666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -701,22 +701,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.07242424242424242</v>
+        <v>0.04021739130434783</v>
       </c>
       <c r="H3">
-        <v>0.07242424242424242</v>
+        <v>0.04021739130434783</v>
       </c>
       <c r="I3">
-        <v>0.07939393939393941</v>
+        <v>0.07782608695652174</v>
       </c>
       <c r="J3">
-        <v>0.0622585567909309</v>
+        <v>0.06597854615999087</v>
       </c>
       <c r="K3">
-        <v>0.192</v>
+        <v>0.323</v>
       </c>
       <c r="L3">
-        <v>0.05818181818181819</v>
+        <v>0.07021739130434783</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -740,61 +740,61 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>9.720000000000001</v>
+        <v>9.82</v>
       </c>
       <c r="V3">
-        <v>0.9346153846153846</v>
+        <v>0.9177570093457945</v>
       </c>
       <c r="W3">
-        <v>0.08807339449541284</v>
+        <v>0.1318367346938775</v>
       </c>
       <c r="X3">
-        <v>0.05138203451548536</v>
+        <v>0.05681300993455153</v>
       </c>
       <c r="Y3">
-        <v>0.03669135997992747</v>
+        <v>0.07502372475932602</v>
       </c>
       <c r="AB3">
-        <v>0.05117551431462832</v>
+        <v>0.05593115147940682</v>
       </c>
       <c r="AD3">
-        <v>0.99</v>
+        <v>3.63</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.99</v>
+        <v>3.63</v>
       </c>
       <c r="AG3">
-        <v>-8.73</v>
+        <v>-6.19</v>
       </c>
       <c r="AH3">
-        <v>0.08691834942932396</v>
+        <v>0.2533147243545011</v>
       </c>
       <c r="AI3">
-        <v>0.2877906976744186</v>
+        <v>0.55</v>
       </c>
       <c r="AJ3">
-        <v>-5.227544910179641</v>
+        <v>-1.372505543237251</v>
       </c>
       <c r="AK3">
-        <v>1.390127388535032</v>
+        <v>1.922360248447205</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.017</v>
+        <v>-0.024</v>
       </c>
       <c r="AN3">
-        <v>3.03680981595092</v>
+        <v>7.484536082474227</v>
       </c>
       <c r="AP3">
-        <v>-26.77914110429448</v>
+        <v>-12.76288659793815</v>
       </c>
       <c r="AQ3">
-        <v>-15.41176470588235</v>
+        <v>-14.91666666666667</v>
       </c>
     </row>
   </sheetData>
